--- a/assessment_forms/049_proportional_reasoning_assessment--assessment_forms.xlsx
+++ b/assessment_forms/049_proportional_reasoning_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,73 +515,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Proportional Reasoning Assessment</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is a ratio?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A ratio is a way to compare two or more numbers</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>intro_question1</t>
+          <t>proportional_relationships</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is a ratio</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Types of Proportional Relationships</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>e.g. equivalent, greater than, less than</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>select_proportional_relationship</t>
+          <t>example_proportion_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Types of Proportional Relationships</t>
+          <t>Example of Proportion</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>e.g. equivalent, greater than, less than, etc.</t>
+          <t>e.g. 1 -2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -593,49 +601,49 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>example_proportion_1</t>
+          <t>example_proportion_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Example of Proportion</t>
+          <t>Another Example of Proportion</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>e.g. 1:2</t>
+          <t>e.g. 2 -4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>example_proportion_2</t>
+          <t>ratio_interpretation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Example of Proportion</t>
+          <t>Ratio Interpretation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>e.g. 2:4</t>
+          <t>e.g. 3 -2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -647,22 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ratio_interpretation_question1</t>
+          <t>answer1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ratio Interpretation</t>
+          <t>Answer 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>e.g. 3:2</t>
+          <t>Please provide a short answer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -674,22 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ratio_interpretation_question2</t>
+          <t>answer2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ratio Interpretation</t>
+          <t>Answer 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>e.g. 5:1</t>
+          <t>Please provide a short answer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -701,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>answer1</t>
+          <t>answer3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Answer 1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Answer 3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide a short answer</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -724,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>answer2</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Answer 2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide a short conclusion</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -747,35 +763,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>answer3</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Answer 3</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ratio_proportion_explanation_1</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Proportion Explanation</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -793,18 +809,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ratio_proportion_explanation_2</t>
+          <t>ratio_interpretation_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Proportion Explanation</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Ratio Interpretation 1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>e.g. 3 -2</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -816,18 +836,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ratio_proportion_explanation_3</t>
+          <t>ratio_interpretation_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Proportion Explanation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Another Ratio Interpretation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>e.g. 5 -1</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -839,18 +863,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ratio_proportion_explanation_4</t>
+          <t>is_ratio_equivalent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Proportion Explanation</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Is the Ratio Equivalent?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Is the ratio equivalent or not?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -862,41 +890,99 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>is_proportion_explanations</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Proportion Explanation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please explain the proportion</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>is_proportion_explanations_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Another Proportion Explanation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please explain another proportion</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>final_conclusion</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Final Conclusion</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please provide a short final conclusion</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>submit_button</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Submit Button</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,10 +997,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -939,7 +1025,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_proportional_relationship_choices</t>
+          <t>proportional_relationships_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -956,7 +1042,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_proportional_relationship_choices</t>
+          <t>proportional_relationships_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -973,7 +1059,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_proportional_relationship_choices</t>
+          <t>proportional_relationships_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -990,17 +1076,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_proportional_relationship_choices</t>
+          <t>example_proportion_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>etc.</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>etc.</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1098,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1029,29 +1115,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>example_proportion_1_choices</t>
+          <t>example_proportion_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1149,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1080,29 +1166,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>example_proportion_2_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>false</t>
+          <t>False</t>
         </is>
       </c>
     </row>
